--- a/data/H131_20260620_14.xlsx
+++ b/data/H131_20260620_14.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>699.0</v>
+        <v>726.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,13 +610,13 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>699.0</v>
+        <v>726.0</v>
       </c>
       <c r="O4" s="2">
-        <v>360.0</v>
+        <v>385.0</v>
       </c>
       <c r="P4" s="2">
-        <v>339.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0</v>
@@ -740,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>814.0</v>
+        <v>830.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -752,22 +752,22 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>814.0</v>
+        <v>830.0</v>
       </c>
       <c r="O6" s="2">
-        <v>436.0</v>
+        <v>444.0</v>
       </c>
       <c r="P6" s="2">
-        <v>378.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0</v>
       </c>
       <c r="R6" s="2">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="S6" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="T6" s="2">
         <v>1.0</v>
@@ -779,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="W6" s="2">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>577.0</v>
+        <v>578.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -894,10 +894,10 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>577.0</v>
+        <v>578.0</v>
       </c>
       <c r="O8" s="2">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="P8" s="2">
         <v>241.0</v>
@@ -953,7 +953,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -965,10 +965,10 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="O9" s="2">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
       <c r="P9" s="2">
         <v>282.0</v>
@@ -1024,7 +1024,7 @@
         <v>311.0</v>
       </c>
       <c r="J10" s="2">
-        <v>231.0</v>
+        <v>237.0</v>
       </c>
       <c r="K10" s="2">
         <v>1.0</v>
@@ -1036,13 +1036,13 @@
         <v>0.0</v>
       </c>
       <c r="N10" s="2">
-        <v>231.0</v>
+        <v>237.0</v>
       </c>
       <c r="O10" s="2">
-        <v>102.0</v>
+        <v>107.0</v>
       </c>
       <c r="P10" s="2">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="Q10" s="2">
         <v>2.0</v>
@@ -1051,7 +1051,7 @@
         <v>9.0</v>
       </c>
       <c r="S10" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="T10" s="2">
         <v>0.0</v>
@@ -1063,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="W10" s="2">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="11">
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>1172.0</v>
+        <v>1207.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,13 +1320,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>1172.0</v>
+        <v>1207.0</v>
       </c>
       <c r="O14" s="2">
-        <v>663.0</v>
+        <v>682.0</v>
       </c>
       <c r="P14" s="2">
-        <v>507.0</v>
+        <v>523.0</v>
       </c>
       <c r="Q14" s="2">
         <v>2.0</v>
@@ -1335,7 +1335,7 @@
         <v>36.0</v>
       </c>
       <c r="S14" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="T14" s="2">
         <v>4.0</v>
@@ -1347,7 +1347,7 @@
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="15">
@@ -1412,13 +1412,13 @@
         <v>0.0</v>
       </c>
       <c r="U15" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="V15" s="2">
         <v>0.0</v>
       </c>
       <c r="W15" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="16">
@@ -1521,7 +1521,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>736.0</v>
+        <v>745.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1533,19 +1533,19 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>736.0</v>
+        <v>745.0</v>
       </c>
       <c r="O17" s="2">
-        <v>407.0</v>
+        <v>412.0</v>
       </c>
       <c r="P17" s="2">
-        <v>327.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q17" s="2">
         <v>2.0</v>
       </c>
       <c r="R17" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="S17" s="2">
         <v>17.0</v>
@@ -1560,7 +1560,7 @@
         <v>0.0</v>
       </c>
       <c r="W17" s="2">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="18">
@@ -1592,7 +1592,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1128.0</v>
+        <v>1129.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1604,10 +1604,10 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1128.0</v>
+        <v>1129.0</v>
       </c>
       <c r="O18" s="2">
-        <v>600.0</v>
+        <v>601.0</v>
       </c>
       <c r="P18" s="2">
         <v>528.0</v>
@@ -1625,13 +1625,13 @@
         <v>7.0</v>
       </c>
       <c r="U18" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="V18" s="2">
         <v>2.0</v>
       </c>
       <c r="W18" s="2">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="19">
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>816.0</v>
+        <v>850.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,25 +1675,25 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>816.0</v>
+        <v>850.0</v>
       </c>
       <c r="O19" s="2">
-        <v>431.0</v>
+        <v>458.0</v>
       </c>
       <c r="P19" s="2">
-        <v>385.0</v>
+        <v>391.0</v>
       </c>
       <c r="Q19" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R19" s="2">
         <v>32.0</v>
       </c>
       <c r="S19" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="T19" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U19" s="2">
         <v>1.0</v>
@@ -1702,7 +1702,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1734,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" s="2">
-        <v>1152.0</v>
+        <v>1177.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1746,25 +1746,25 @@
         <v>1.0</v>
       </c>
       <c r="N20" s="2">
-        <v>1151.0</v>
+        <v>1176.0</v>
       </c>
       <c r="O20" s="2">
-        <v>648.0</v>
+        <v>662.0</v>
       </c>
       <c r="P20" s="2">
-        <v>491.0</v>
+        <v>502.0</v>
       </c>
       <c r="Q20" s="2">
         <v>13.0</v>
       </c>
       <c r="R20" s="2">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="S20" s="2">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
       <c r="T20" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="U20" s="2">
         <v>0.0</v>
@@ -1773,7 +1773,7 @@
         <v>0.0</v>
       </c>
       <c r="W20" s="2">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1805,7 +1805,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" s="2">
-        <v>742.0</v>
+        <v>746.0</v>
       </c>
       <c r="K21" s="2">
         <v>1.0</v>
@@ -1817,13 +1817,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <v>742.0</v>
+        <v>746.0</v>
       </c>
       <c r="O21" s="2">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
       <c r="P21" s="2">
-        <v>354.0</v>
+        <v>356.0</v>
       </c>
       <c r="Q21" s="2">
         <v>0.0</v>
@@ -1832,19 +1832,19 @@
         <v>37.0</v>
       </c>
       <c r="S21" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="T21" s="2">
         <v>4.0</v>
       </c>
       <c r="U21" s="2">
-        <v>51.0</v>
+        <v>65.0</v>
       </c>
       <c r="V21" s="2">
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>123.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1909,13 +1909,13 @@
         <v>0.0</v>
       </c>
       <c r="U22" s="2">
-        <v>21.0</v>
+        <v>53.0</v>
       </c>
       <c r="V22" s="2">
         <v>0.0</v>
       </c>
       <c r="W22" s="2">
-        <v>73.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1947,7 +1947,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>470.0</v>
+        <v>569.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1959,13 +1959,13 @@
         <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>470.0</v>
+        <v>569.0</v>
       </c>
       <c r="O23" s="2">
-        <v>238.0</v>
+        <v>285.0</v>
       </c>
       <c r="P23" s="2">
-        <v>232.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q23" s="2">
         <v>0.0</v>
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>923.0</v>
+        <v>1026.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>923.0</v>
+        <v>1026.0</v>
       </c>
       <c r="O24" s="2">
-        <v>540.0</v>
+        <v>606.0</v>
       </c>
       <c r="P24" s="2">
-        <v>367.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q24" s="2">
         <v>16.0</v>
@@ -2160,7 +2160,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" s="2">
-        <v>1217.0</v>
+        <v>1228.0</v>
       </c>
       <c r="K26" s="2">
         <v>1.0</v>
@@ -2172,10 +2172,10 @@
         <v>0.0</v>
       </c>
       <c r="N26" s="2">
-        <v>1217.0</v>
+        <v>1228.0</v>
       </c>
       <c r="O26" s="2">
-        <v>662.0</v>
+        <v>673.0</v>
       </c>
       <c r="P26" s="2">
         <v>555.0</v>
@@ -2184,22 +2184,22 @@
         <v>0.0</v>
       </c>
       <c r="R26" s="2">
-        <v>0.0</v>
+        <v>47.0</v>
       </c>
       <c r="S26" s="2">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="T26" s="2">
         <v>0.0</v>
       </c>
       <c r="U26" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="V26" s="2">
         <v>0.0</v>
       </c>
       <c r="W26" s="2">
-        <v>0.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -2302,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1075.0</v>
+        <v>1097.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2314,13 +2314,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1075.0</v>
+        <v>1097.0</v>
       </c>
       <c r="O28" s="2">
-        <v>597.0</v>
+        <v>611.0</v>
       </c>
       <c r="P28" s="2">
-        <v>476.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
@@ -2373,7 +2373,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>761.0</v>
+        <v>772.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2385,13 +2385,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>761.0</v>
+        <v>772.0</v>
       </c>
       <c r="O29" s="2">
-        <v>227.0</v>
+        <v>237.0</v>
       </c>
       <c r="P29" s="2">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q29" s="2">
         <v>132.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>1044.0</v>
+        <v>1067.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,34 +2527,34 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>1044.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O31" s="2">
-        <v>571.0</v>
+        <v>584.0</v>
       </c>
       <c r="P31" s="2">
-        <v>461.0</v>
+        <v>470.0</v>
       </c>
       <c r="Q31" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R31" s="2">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="S31" s="2">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="T31" s="2">
         <v>0.0</v>
       </c>
       <c r="U31" s="2">
-        <v>31.0</v>
+        <v>45.0</v>
       </c>
       <c r="V31" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="W31" s="2">
-        <v>107.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -2610,13 +2610,13 @@
         <v>21.0</v>
       </c>
       <c r="R32" s="2">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="S32" s="2">
         <v>3.0</v>
       </c>
       <c r="T32" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U32" s="2">
         <v>0.0</v>
@@ -2625,7 +2625,7 @@
         <v>0.0</v>
       </c>
       <c r="W32" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,10 +2811,10 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="O35" s="2">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="P35" s="2">
         <v>222.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>736.0</v>
+        <v>737.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,10 +2882,10 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>736.0</v>
+        <v>737.0</v>
       </c>
       <c r="O36" s="2">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="P36" s="2">
         <v>376.0</v>
@@ -3012,7 +3012,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>986.0</v>
+        <v>999.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3024,22 +3024,22 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>986.0</v>
+        <v>999.0</v>
       </c>
       <c r="O38" s="2">
-        <v>578.0</v>
+        <v>584.0</v>
       </c>
       <c r="P38" s="2">
-        <v>408.0</v>
+        <v>412.0</v>
       </c>
       <c r="Q38" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="R38" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="S38" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="T38" s="2">
         <v>3.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="W38" s="2">
-        <v>43.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -3083,7 +3083,7 @@
         <v>588.0</v>
       </c>
       <c r="J39" s="2">
-        <v>532.0</v>
+        <v>542.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,13 +3095,13 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>532.0</v>
+        <v>542.0</v>
       </c>
       <c r="O39" s="2">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="P39" s="2">
-        <v>254.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
@@ -3113,7 +3113,7 @@
         <v>14.0</v>
       </c>
       <c r="T39" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U39" s="2">
         <v>0.0</v>
@@ -3122,7 +3122,7 @@
         <v>0.0</v>
       </c>
       <c r="W39" s="2">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -3225,7 +3225,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>1059.0</v>
+        <v>1082.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3237,10 +3237,10 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>1059.0</v>
+        <v>1082.0</v>
       </c>
       <c r="O41" s="2">
-        <v>543.0</v>
+        <v>566.0</v>
       </c>
       <c r="P41" s="2">
         <v>516.0</v>
@@ -3255,7 +3255,7 @@
         <v>8.0</v>
       </c>
       <c r="T41" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U41" s="2">
         <v>0.0</v>
@@ -3264,7 +3264,7 @@
         <v>0.0</v>
       </c>
       <c r="W41" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>759.0</v>
+        <v>789.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,25 +3308,25 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>759.0</v>
+        <v>789.0</v>
       </c>
       <c r="O42" s="2">
-        <v>503.0</v>
+        <v>518.0</v>
       </c>
       <c r="P42" s="2">
-        <v>255.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q42" s="2">
         <v>1.0</v>
       </c>
       <c r="R42" s="2">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="S42" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T42" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U42" s="2">
         <v>0.0</v>
@@ -3335,7 +3335,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1095.0</v>
+        <v>1097.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,16 +3521,16 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1094.0</v>
+        <v>1096.0</v>
       </c>
       <c r="O45" s="2">
         <v>514.0</v>
       </c>
       <c r="P45" s="2">
-        <v>542.0</v>
+        <v>543.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="R45" s="2">
         <v>52.0</v>
@@ -3651,7 +3651,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" s="2">
-        <v>734.0</v>
+        <v>753.0</v>
       </c>
       <c r="K47" s="2">
         <v>1.0</v>
@@ -3663,16 +3663,16 @@
         <v>0.0</v>
       </c>
       <c r="N47" s="2">
-        <v>734.0</v>
+        <v>753.0</v>
       </c>
       <c r="O47" s="2">
-        <v>400.0</v>
+        <v>402.0</v>
       </c>
       <c r="P47" s="2">
-        <v>333.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q47" s="2">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="R47" s="2">
         <v>23.0</v>
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>968.0</v>
+        <v>995.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,13 +3734,13 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>968.0</v>
+        <v>995.0</v>
       </c>
       <c r="O48" s="2">
-        <v>570.0</v>
+        <v>595.0</v>
       </c>
       <c r="P48" s="2">
-        <v>398.0</v>
+        <v>400.0</v>
       </c>
       <c r="Q48" s="2">
         <v>0.0</v>
@@ -3752,7 +3752,7 @@
         <v>4.0</v>
       </c>
       <c r="T48" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U48" s="2">
         <v>10.0</v>
@@ -3761,7 +3761,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>1196.0</v>
+        <v>1223.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,13 +3805,13 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>1196.0</v>
+        <v>1223.0</v>
       </c>
       <c r="O49" s="2">
-        <v>670.0</v>
+        <v>689.0</v>
       </c>
       <c r="P49" s="2">
-        <v>491.0</v>
+        <v>499.0</v>
       </c>
       <c r="Q49" s="2">
         <v>35.0</v>
@@ -4219,7 +4219,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" s="2">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="K55" s="2">
         <v>1.0</v>
@@ -4231,7 +4231,7 @@
         <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="O55" s="2">
         <v>227.0</v>
@@ -4240,7 +4240,7 @@
         <v>243.0</v>
       </c>
       <c r="Q55" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="R55" s="2">
         <v>19.0</v>
@@ -4462,7 +4462,7 @@
         <v>0.0</v>
       </c>
       <c r="T58" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U58" s="2">
         <v>0.0</v>
@@ -4471,7 +4471,7 @@
         <v>0.0</v>
       </c>
       <c r="W58" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
@@ -4503,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>712.0</v>
+        <v>764.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4515,13 +4515,13 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>712.0</v>
+        <v>764.0</v>
       </c>
       <c r="O59" s="2">
-        <v>345.0</v>
+        <v>382.0</v>
       </c>
       <c r="P59" s="2">
-        <v>366.0</v>
+        <v>381.0</v>
       </c>
       <c r="Q59" s="2">
         <v>1.0</v>
@@ -4533,7 +4533,7 @@
         <v>17.0</v>
       </c>
       <c r="T59" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U59" s="2">
         <v>3.0</v>
@@ -4542,7 +4542,7 @@
         <v>0.0</v>
       </c>
       <c r="W59" s="2">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -4787,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>1023.0</v>
+        <v>1047.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4799,13 +4799,13 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>1023.0</v>
+        <v>1047.0</v>
       </c>
       <c r="O63" s="2">
-        <v>617.0</v>
+        <v>638.0</v>
       </c>
       <c r="P63" s="2">
-        <v>405.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q63" s="2">
         <v>1.0</v>
@@ -4858,7 +4858,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" s="2">
-        <v>1078.0</v>
+        <v>1080.0</v>
       </c>
       <c r="K64" s="2">
         <v>1.0</v>
@@ -4870,10 +4870,10 @@
         <v>0.0</v>
       </c>
       <c r="N64" s="2">
-        <v>1078.0</v>
+        <v>1080.0</v>
       </c>
       <c r="O64" s="2">
-        <v>617.0</v>
+        <v>619.0</v>
       </c>
       <c r="P64" s="2">
         <v>461.0</v>
@@ -5302,10 +5302,10 @@
         <v>695.0</v>
       </c>
       <c r="P70" s="2">
-        <v>412.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q70" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R70" s="2">
         <v>12.0</v>
@@ -5781,7 +5781,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>606.0</v>
+        <v>620.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5793,10 +5793,10 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>606.0</v>
+        <v>620.0</v>
       </c>
       <c r="O77" s="2">
-        <v>141.0</v>
+        <v>155.0</v>
       </c>
       <c r="P77" s="2">
         <v>308.0</v>
@@ -5805,7 +5805,7 @@
         <v>157.0</v>
       </c>
       <c r="R77" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="S77" s="2">
         <v>0.0</v>
@@ -5820,7 +5820,7 @@
         <v>0.0</v>
       </c>
       <c r="W77" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>766.0</v>
+        <v>767.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,10 +5864,10 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>766.0</v>
+        <v>767.0</v>
       </c>
       <c r="O78" s="2">
-        <v>307.0</v>
+        <v>308.0</v>
       </c>
       <c r="P78" s="2">
         <v>459.0</v>
@@ -5876,7 +5876,7 @@
         <v>0.0</v>
       </c>
       <c r="R78" s="2">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="S78" s="2">
         <v>0.0</v>
@@ -5891,7 +5891,7 @@
         <v>0.0</v>
       </c>
       <c r="W78" s="2">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -5923,7 +5923,7 @@
         <v>787.0</v>
       </c>
       <c r="J79" s="2">
-        <v>620.0</v>
+        <v>639.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5935,13 +5935,13 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>620.0</v>
+        <v>639.0</v>
       </c>
       <c r="O79" s="2">
-        <v>369.0</v>
+        <v>387.0</v>
       </c>
       <c r="P79" s="2">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="Q79" s="2">
         <v>0.0</v>
@@ -5950,7 +5950,7 @@
         <v>20.0</v>
       </c>
       <c r="S79" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="T79" s="2">
         <v>0.0</v>
@@ -5962,7 +5962,7 @@
         <v>0.0</v>
       </c>
       <c r="W79" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -6021,10 +6021,10 @@
         <v>3.0</v>
       </c>
       <c r="S80" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T80" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U80" s="2">
         <v>0.0</v>
@@ -6033,7 +6033,7 @@
         <v>0.0</v>
       </c>
       <c r="W80" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
@@ -6098,13 +6098,13 @@
         <v>4.0</v>
       </c>
       <c r="U81" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V81" s="2">
         <v>0.0</v>
       </c>
       <c r="W81" s="2">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>714.0</v>
+        <v>745.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,34 +6645,34 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>714.0</v>
+        <v>745.0</v>
       </c>
       <c r="O89" s="2">
-        <v>400.0</v>
+        <v>417.0</v>
       </c>
       <c r="P89" s="2">
-        <v>314.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q89" s="2">
         <v>0.0</v>
       </c>
       <c r="R89" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="S89" s="2">
         <v>21.0</v>
       </c>
-      <c r="S89" s="2">
-        <v>16.0</v>
-      </c>
       <c r="T89" s="2">
         <v>0.0</v>
       </c>
       <c r="U89" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="V89" s="2">
         <v>0.0</v>
       </c>
       <c r="W89" s="2">
-        <v>46.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -6846,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>809.0</v>
+        <v>819.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6858,13 +6858,13 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>809.0</v>
+        <v>819.0</v>
       </c>
       <c r="O92" s="2">
-        <v>386.0</v>
+        <v>392.0</v>
       </c>
       <c r="P92" s="2">
-        <v>323.0</v>
+        <v>327.0</v>
       </c>
       <c r="Q92" s="2">
         <v>100.0</v>
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>853.0</v>
+        <v>856.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,10 +6929,10 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>853.0</v>
+        <v>856.0</v>
       </c>
       <c r="O93" s="2">
-        <v>490.0</v>
+        <v>493.0</v>
       </c>
       <c r="P93" s="2">
         <v>362.0</v>
@@ -6947,7 +6947,7 @@
         <v>20.0</v>
       </c>
       <c r="T93" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U93" s="2">
         <v>0.0</v>
@@ -6956,7 +6956,7 @@
         <v>2.0</v>
       </c>
       <c r="W93" s="2">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>1118.0</v>
+        <v>1219.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,16 +7142,16 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>1118.0</v>
+        <v>1219.0</v>
       </c>
       <c r="O96" s="2">
-        <v>627.0</v>
+        <v>711.0</v>
       </c>
       <c r="P96" s="2">
-        <v>485.0</v>
+        <v>495.0</v>
       </c>
       <c r="Q96" s="2">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="R96" s="2">
         <v>1.0</v>
@@ -7201,7 +7201,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" s="2">
-        <v>947.0</v>
+        <v>954.0</v>
       </c>
       <c r="K97" s="2">
         <v>1.0</v>
@@ -7213,13 +7213,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" s="2">
-        <v>947.0</v>
+        <v>954.0</v>
       </c>
       <c r="O97" s="2">
-        <v>477.0</v>
+        <v>479.0</v>
       </c>
       <c r="P97" s="2">
-        <v>452.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q97" s="2">
         <v>18.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1033.0</v>
+        <v>1094.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,13 +7284,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1033.0</v>
+        <v>1094.0</v>
       </c>
       <c r="O98" s="2">
-        <v>534.0</v>
+        <v>571.0</v>
       </c>
       <c r="P98" s="2">
-        <v>489.0</v>
+        <v>513.0</v>
       </c>
       <c r="Q98" s="2">
         <v>10.0</v>
@@ -7302,7 +7302,7 @@
         <v>11.0</v>
       </c>
       <c r="T98" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U98" s="2">
         <v>0.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7343,7 +7343,7 @@
         <v>880.0</v>
       </c>
       <c r="J99" s="2">
-        <v>798.0</v>
+        <v>804.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,13 +7355,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>798.0</v>
+        <v>804.0</v>
       </c>
       <c r="O99" s="2">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="P99" s="2">
-        <v>385.0</v>
+        <v>390.0</v>
       </c>
       <c r="Q99" s="2">
         <v>0.0</v>
@@ -7370,10 +7370,10 @@
         <v>39.0</v>
       </c>
       <c r="S99" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="T99" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="U99" s="2">
         <v>0.0</v>
@@ -7382,7 +7382,7 @@
         <v>0.0</v>
       </c>
       <c r="W99" s="2">
-        <v>55.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1238.0</v>
+        <v>1244.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,13 +7426,13 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1238.0</v>
+        <v>1244.0</v>
       </c>
       <c r="O100" s="2">
-        <v>602.0</v>
+        <v>607.0</v>
       </c>
       <c r="P100" s="2">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
       <c r="Q100" s="2">
         <v>2.0</v>
@@ -7556,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>1022.0</v>
+        <v>1031.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7568,10 +7568,10 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>1022.0</v>
+        <v>1031.0</v>
       </c>
       <c r="O102" s="2">
-        <v>539.0</v>
+        <v>548.0</v>
       </c>
       <c r="P102" s="2">
         <v>483.0</v>
@@ -7583,7 +7583,7 @@
         <v>56.0</v>
       </c>
       <c r="S102" s="2">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="T102" s="2">
         <v>0.0</v>
@@ -7595,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" s="2">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>589.0</v>
+        <v>594.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,22 +7639,22 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>589.0</v>
+        <v>594.0</v>
       </c>
       <c r="O103" s="2">
-        <v>344.0</v>
+        <v>345.0</v>
       </c>
       <c r="P103" s="2">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="Q103" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="R103" s="2">
         <v>24.0</v>
       </c>
       <c r="S103" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="T103" s="2">
         <v>0.0</v>
@@ -7666,7 +7666,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -7911,7 +7911,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>754.0</v>
+        <v>765.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7923,13 +7923,13 @@
         <v>0.0</v>
       </c>
       <c r="N107" s="2">
-        <v>754.0</v>
+        <v>765.0</v>
       </c>
       <c r="O107" s="2">
-        <v>397.0</v>
+        <v>402.0</v>
       </c>
       <c r="P107" s="2">
-        <v>357.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -7982,7 +7982,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>729.0</v>
+        <v>736.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -7994,13 +7994,13 @@
         <v>1.0</v>
       </c>
       <c r="N108" s="2">
-        <v>728.0</v>
+        <v>735.0</v>
       </c>
       <c r="O108" s="2">
-        <v>457.0</v>
+        <v>462.0</v>
       </c>
       <c r="P108" s="2">
-        <v>272.0</v>
+        <v>274.0</v>
       </c>
       <c r="Q108" s="2">
         <v>0.0</v>
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>585.0</v>
+        <v>599.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,22 +8136,22 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>585.0</v>
+        <v>599.0</v>
       </c>
       <c r="O110" s="2">
-        <v>296.0</v>
+        <v>305.0</v>
       </c>
       <c r="P110" s="2">
-        <v>287.0</v>
+        <v>290.0</v>
       </c>
       <c r="Q110" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R110" s="2">
         <v>47.0</v>
       </c>
       <c r="S110" s="2">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="T110" s="2">
         <v>1.0</v>
@@ -8163,7 +8163,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" s="2">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,13 +8278,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="O112" s="2">
         <v>307.0</v>
       </c>
       <c r="P112" s="2">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
       <c r="Q112" s="2">
         <v>7.0</v>
@@ -8293,7 +8293,7 @@
         <v>11.0</v>
       </c>
       <c r="S112" s="2">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="T112" s="2">
         <v>5.0</v>
@@ -8305,7 +8305,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>733.0</v>
+        <v>780.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,13 +8349,13 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>733.0</v>
+        <v>780.0</v>
       </c>
       <c r="O113" s="2">
-        <v>309.0</v>
+        <v>355.0</v>
       </c>
       <c r="P113" s="2">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="Q113" s="2">
         <v>0.0</v>
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>675.0</v>
+        <v>709.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,19 +8420,19 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>675.0</v>
+        <v>709.0</v>
       </c>
       <c r="O114" s="2">
-        <v>387.0</v>
+        <v>413.0</v>
       </c>
       <c r="P114" s="2">
-        <v>287.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
       </c>
       <c r="R114" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="S114" s="2">
         <v>0.0</v>
@@ -8447,7 +8447,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>729.0</v>
+        <v>731.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,10 +8633,10 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>728.0</v>
+        <v>730.0</v>
       </c>
       <c r="O117" s="2">
-        <v>356.0</v>
+        <v>358.0</v>
       </c>
       <c r="P117" s="2">
         <v>373.0</v>
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>694.0</v>
+        <v>714.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,13 +8846,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>694.0</v>
+        <v>714.0</v>
       </c>
       <c r="O120" s="2">
-        <v>373.0</v>
+        <v>387.0</v>
       </c>
       <c r="P120" s="2">
-        <v>318.0</v>
+        <v>324.0</v>
       </c>
       <c r="Q120" s="2">
         <v>3.0</v>
@@ -8861,7 +8861,7 @@
         <v>39.0</v>
       </c>
       <c r="S120" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T120" s="2">
         <v>0.0</v>
@@ -8873,7 +8873,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>779.0</v>
+        <v>835.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,13 +8917,13 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>779.0</v>
+        <v>835.0</v>
       </c>
       <c r="O121" s="2">
-        <v>500.0</v>
+        <v>538.0</v>
       </c>
       <c r="P121" s="2">
-        <v>279.0</v>
+        <v>297.0</v>
       </c>
       <c r="Q121" s="2">
         <v>0.0</v>
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>950.0</v>
+        <v>970.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9272,22 +9272,22 @@
         <v>0.0</v>
       </c>
       <c r="N126" s="2">
-        <v>950.0</v>
+        <v>970.0</v>
       </c>
       <c r="O126" s="2">
-        <v>494.0</v>
+        <v>502.0</v>
       </c>
       <c r="P126" s="2">
-        <v>425.0</v>
+        <v>436.0</v>
       </c>
       <c r="Q126" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="R126" s="2">
         <v>19.0</v>
       </c>
       <c r="S126" s="2">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
       <c r="T126" s="2">
         <v>1.0</v>
@@ -9299,7 +9299,7 @@
         <v>1.0</v>
       </c>
       <c r="W126" s="2">
-        <v>54.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>974.0</v>
+        <v>1016.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,34 +9343,34 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>974.0</v>
+        <v>1016.0</v>
       </c>
       <c r="O127" s="2">
-        <v>616.0</v>
+        <v>635.0</v>
       </c>
       <c r="P127" s="2">
-        <v>358.0</v>
+        <v>381.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
       </c>
       <c r="R127" s="2">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="S127" s="2">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="T127" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U127" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>91.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>1107.0</v>
+        <v>1133.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,34 +9414,34 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>1107.0</v>
+        <v>1133.0</v>
       </c>
       <c r="O128" s="2">
-        <v>623.0</v>
+        <v>642.0</v>
       </c>
       <c r="P128" s="2">
-        <v>481.0</v>
+        <v>487.0</v>
       </c>
       <c r="Q128" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R128" s="2">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="S128" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="T128" s="2">
         <v>0.0</v>
       </c>
       <c r="U128" s="2">
-        <v>47.0</v>
+        <v>57.0</v>
       </c>
       <c r="V128" s="2">
         <v>0.0</v>
       </c>
       <c r="W128" s="2">
-        <v>98.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>752.0</v>
+        <v>826.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,22 +9485,22 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>752.0</v>
+        <v>826.0</v>
       </c>
       <c r="O129" s="2">
-        <v>514.0</v>
+        <v>562.0</v>
       </c>
       <c r="P129" s="2">
-        <v>236.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q129" s="2">
         <v>2.0</v>
       </c>
       <c r="R129" s="2">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="S129" s="2">
-        <v>46.0</v>
+        <v>62.0</v>
       </c>
       <c r="T129" s="2">
         <v>0.0</v>
@@ -9512,7 +9512,7 @@
         <v>0.0</v>
       </c>
       <c r="W129" s="2">
-        <v>109.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
@@ -9544,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>677.0</v>
+        <v>697.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9556,16 +9556,16 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>675.0</v>
+        <v>695.0</v>
       </c>
       <c r="O130" s="2">
-        <v>447.0</v>
+        <v>461.0</v>
       </c>
       <c r="P130" s="2">
-        <v>197.0</v>
+        <v>200.0</v>
       </c>
       <c r="Q130" s="2">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="R130" s="2">
         <v>29.0</v>
@@ -9686,7 +9686,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" s="2">
-        <v>775.0</v>
+        <v>804.0</v>
       </c>
       <c r="K132" s="2">
         <v>1.0</v>
@@ -9698,16 +9698,16 @@
         <v>0.0</v>
       </c>
       <c r="N132" s="2">
-        <v>775.0</v>
+        <v>804.0</v>
       </c>
       <c r="O132" s="2">
-        <v>377.0</v>
+        <v>401.0</v>
       </c>
       <c r="P132" s="2">
-        <v>384.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q132" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R132" s="2">
         <v>24.0</v>
@@ -9719,13 +9719,13 @@
         <v>0.0</v>
       </c>
       <c r="U132" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="V132" s="2">
         <v>0.0</v>
       </c>
       <c r="W132" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -9757,7 +9757,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" s="2">
-        <v>1059.0</v>
+        <v>1067.0</v>
       </c>
       <c r="K133" s="2">
         <v>1.0</v>
@@ -9769,19 +9769,19 @@
         <v>0.0</v>
       </c>
       <c r="N133" s="2">
-        <v>1059.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O133" s="2">
-        <v>559.0</v>
+        <v>561.0</v>
       </c>
       <c r="P133" s="2">
-        <v>487.0</v>
+        <v>493.0</v>
       </c>
       <c r="Q133" s="2">
         <v>13.0</v>
       </c>
       <c r="R133" s="2">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="S133" s="2">
         <v>0.0</v>
@@ -9796,7 +9796,7 @@
         <v>0.0</v>
       </c>
       <c r="W133" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>1069.0</v>
+        <v>1100.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,13 +9911,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>1068.0</v>
+        <v>1099.0</v>
       </c>
       <c r="O135" s="2">
-        <v>576.0</v>
+        <v>603.0</v>
       </c>
       <c r="P135" s="2">
-        <v>409.0</v>
+        <v>413.0</v>
       </c>
       <c r="Q135" s="2">
         <v>84.0</v>
@@ -9932,13 +9932,13 @@
         <v>0.0</v>
       </c>
       <c r="U135" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="V135" s="2">
         <v>0.0</v>
       </c>
       <c r="W135" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>913.0</v>
+        <v>914.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,10 +9982,10 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>913.0</v>
+        <v>914.0</v>
       </c>
       <c r="O136" s="2">
-        <v>487.0</v>
+        <v>488.0</v>
       </c>
       <c r="P136" s="2">
         <v>411.0</v>
@@ -10112,7 +10112,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" s="2">
-        <v>870.0</v>
+        <v>906.0</v>
       </c>
       <c r="K138" s="2">
         <v>1.0</v>
@@ -10124,13 +10124,13 @@
         <v>0.0</v>
       </c>
       <c r="N138" s="2">
-        <v>870.0</v>
+        <v>906.0</v>
       </c>
       <c r="O138" s="2">
-        <v>521.0</v>
+        <v>552.0</v>
       </c>
       <c r="P138" s="2">
-        <v>325.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q138" s="2">
         <v>24.0</v>
@@ -10139,19 +10139,19 @@
         <v>36.0</v>
       </c>
       <c r="S138" s="2">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
       <c r="T138" s="2">
         <v>3.0</v>
       </c>
       <c r="U138" s="2">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="V138" s="2">
         <v>0.0</v>
       </c>
       <c r="W138" s="2">
-        <v>108.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>903.0</v>
+        <v>911.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,13 +10195,13 @@
         <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>903.0</v>
+        <v>911.0</v>
       </c>
       <c r="O139" s="2">
-        <v>553.0</v>
+        <v>559.0</v>
       </c>
       <c r="P139" s="2">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q139" s="2">
         <v>23.0</v>
@@ -10210,7 +10210,7 @@
         <v>24.0</v>
       </c>
       <c r="S139" s="2">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="T139" s="2">
         <v>0.0</v>
@@ -10222,7 +10222,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" s="2">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>989.0</v>
+        <v>1018.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>989.0</v>
+        <v>1018.0</v>
       </c>
       <c r="O144" s="2">
-        <v>546.0</v>
+        <v>561.0</v>
       </c>
       <c r="P144" s="2">
-        <v>443.0</v>
+        <v>457.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10609,7 +10609,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>726.0</v>
+        <v>728.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10621,10 +10621,10 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>726.0</v>
+        <v>728.0</v>
       </c>
       <c r="O145" s="2">
-        <v>312.0</v>
+        <v>314.0</v>
       </c>
       <c r="P145" s="2">
         <v>389.0</v>
@@ -10822,7 +10822,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>862.0</v>
+        <v>864.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10831,13 +10831,13 @@
         <v>1.0</v>
       </c>
       <c r="M148" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>860.0</v>
+        <v>864.0</v>
       </c>
       <c r="O148" s="2">
-        <v>393.0</v>
+        <v>395.0</v>
       </c>
       <c r="P148" s="2">
         <v>469.0</v>
@@ -10964,7 +10964,7 @@
         <v>971.0</v>
       </c>
       <c r="J150" s="2">
-        <v>830.0</v>
+        <v>888.0</v>
       </c>
       <c r="K150" s="2">
         <v>1.0</v>
@@ -10976,13 +10976,13 @@
         <v>0.0</v>
       </c>
       <c r="N150" s="2">
-        <v>830.0</v>
+        <v>888.0</v>
       </c>
       <c r="O150" s="2">
-        <v>478.0</v>
+        <v>532.0</v>
       </c>
       <c r="P150" s="2">
-        <v>352.0</v>
+        <v>356.0</v>
       </c>
       <c r="Q150" s="2">
         <v>0.0</v>
@@ -11130,7 +11130,7 @@
         <v>0.0</v>
       </c>
       <c r="R152" s="2">
-        <v>18.0</v>
+        <v>76.0</v>
       </c>
       <c r="S152" s="2">
         <v>1.0</v>
@@ -11145,7 +11145,7 @@
         <v>0.0</v>
       </c>
       <c r="W152" s="2">
-        <v>19.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -11177,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>817.0</v>
+        <v>826.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11189,13 +11189,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>817.0</v>
+        <v>826.0</v>
       </c>
       <c r="O153" s="2">
-        <v>400.0</v>
+        <v>404.0</v>
       </c>
       <c r="P153" s="2">
-        <v>416.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q153" s="2">
         <v>1.0</v>
@@ -11319,7 +11319,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" s="2">
-        <v>930.0</v>
+        <v>946.0</v>
       </c>
       <c r="K155" s="2">
         <v>1.0</v>
@@ -11331,25 +11331,25 @@
         <v>0.0</v>
       </c>
       <c r="N155" s="2">
-        <v>930.0</v>
+        <v>946.0</v>
       </c>
       <c r="O155" s="2">
-        <v>458.0</v>
+        <v>468.0</v>
       </c>
       <c r="P155" s="2">
-        <v>471.0</v>
+        <v>477.0</v>
       </c>
       <c r="Q155" s="2">
         <v>1.0</v>
       </c>
       <c r="R155" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="S155" s="2">
         <v>5.0</v>
       </c>
       <c r="T155" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U155" s="2">
         <v>0.0</v>
@@ -11358,7 +11358,7 @@
         <v>0.0</v>
       </c>
       <c r="W155" s="2">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
@@ -11461,7 +11461,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>875.0</v>
+        <v>945.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11473,13 +11473,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>871.0</v>
+        <v>941.0</v>
       </c>
       <c r="O157" s="2">
-        <v>348.0</v>
+        <v>409.0</v>
       </c>
       <c r="P157" s="2">
-        <v>527.0</v>
+        <v>536.0</v>
       </c>
       <c r="Q157" s="2">
         <v>0.0</v>
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>849.0</v>
+        <v>858.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,13 +11544,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>849.0</v>
+        <v>858.0</v>
       </c>
       <c r="O158" s="2">
-        <v>387.0</v>
+        <v>393.0</v>
       </c>
       <c r="P158" s="2">
-        <v>462.0</v>
+        <v>465.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>886.0</v>
+        <v>903.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>885.0</v>
+        <v>902.0</v>
       </c>
       <c r="O159" s="2">
-        <v>514.0</v>
+        <v>523.0</v>
       </c>
       <c r="P159" s="2">
-        <v>372.0</v>
+        <v>380.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11674,7 +11674,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>1030.0</v>
+        <v>1035.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11686,13 +11686,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>1030.0</v>
+        <v>1035.0</v>
       </c>
       <c r="O160" s="2">
-        <v>521.0</v>
+        <v>523.0</v>
       </c>
       <c r="P160" s="2">
-        <v>509.0</v>
+        <v>512.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>965.0</v>
+        <v>1004.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,13 +11757,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>965.0</v>
+        <v>1004.0</v>
       </c>
       <c r="O161" s="2">
-        <v>514.0</v>
+        <v>534.0</v>
       </c>
       <c r="P161" s="2">
-        <v>443.0</v>
+        <v>462.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>855.0</v>
+        <v>866.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,19 +11828,19 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>854.0</v>
+        <v>865.0</v>
       </c>
       <c r="O162" s="2">
-        <v>36.0</v>
+        <v>44.0</v>
       </c>
       <c r="P162" s="2">
-        <v>200.0</v>
+        <v>202.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="R162" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="S162" s="2">
         <v>0.0</v>
@@ -11855,7 +11855,7 @@
         <v>0.0</v>
       </c>
       <c r="W162" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>738.0</v>
+        <v>743.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,34 +11899,34 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>738.0</v>
+        <v>743.0</v>
       </c>
       <c r="O163" s="2">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="P163" s="2">
-        <v>332.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q163" s="2">
         <v>381.0</v>
       </c>
       <c r="R163" s="2">
-        <v>36.0</v>
+        <v>43.0</v>
       </c>
       <c r="S163" s="2">
-        <v>49.0</v>
+        <v>63.0</v>
       </c>
       <c r="T163" s="2">
         <v>0.0</v>
       </c>
       <c r="U163" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V163" s="2">
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>85.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>709.0</v>
+        <v>729.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,13 +12112,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>709.0</v>
+        <v>729.0</v>
       </c>
       <c r="O166" s="2">
-        <v>394.0</v>
+        <v>406.0</v>
       </c>
       <c r="P166" s="2">
-        <v>315.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
@@ -12242,7 +12242,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>683.0</v>
+        <v>688.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12254,13 +12254,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>683.0</v>
+        <v>688.0</v>
       </c>
       <c r="O168" s="2">
-        <v>231.0</v>
+        <v>235.0</v>
       </c>
       <c r="P168" s="2">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q168" s="2">
         <v>88.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>461.0</v>
+        <v>465.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,19 +12325,19 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>461.0</v>
+        <v>465.0</v>
       </c>
       <c r="O169" s="2">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="P169" s="2">
-        <v>212.0</v>
+        <v>214.0</v>
       </c>
       <c r="Q169" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R169" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S169" s="2">
         <v>0.0</v>
@@ -12352,7 +12352,7 @@
         <v>0.0</v>
       </c>
       <c r="W169" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
@@ -12384,7 +12384,7 @@
         <v>968.0</v>
       </c>
       <c r="J170" s="2">
-        <v>774.0</v>
+        <v>792.0</v>
       </c>
       <c r="K170" s="2">
         <v>1.0</v>
@@ -12396,16 +12396,16 @@
         <v>0.0</v>
       </c>
       <c r="N170" s="2">
-        <v>774.0</v>
+        <v>792.0</v>
       </c>
       <c r="O170" s="2">
-        <v>88.0</v>
+        <v>98.0</v>
       </c>
       <c r="P170" s="2">
-        <v>358.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q170" s="2">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="R170" s="2">
         <v>0.0</v>
@@ -12455,7 +12455,7 @@
         <v>576.0</v>
       </c>
       <c r="J171" s="2">
-        <v>453.0</v>
+        <v>476.0</v>
       </c>
       <c r="K171" s="2">
         <v>1.0</v>
@@ -12467,13 +12467,13 @@
         <v>0.0</v>
       </c>
       <c r="N171" s="2">
-        <v>453.0</v>
+        <v>476.0</v>
       </c>
       <c r="O171" s="2">
-        <v>252.0</v>
+        <v>263.0</v>
       </c>
       <c r="P171" s="2">
-        <v>201.0</v>
+        <v>213.0</v>
       </c>
       <c r="Q171" s="2">
         <v>0.0</v>
@@ -12526,7 +12526,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>552.0</v>
+        <v>597.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12538,13 +12538,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>552.0</v>
+        <v>597.0</v>
       </c>
       <c r="O172" s="2">
-        <v>293.0</v>
+        <v>317.0</v>
       </c>
       <c r="P172" s="2">
-        <v>259.0</v>
+        <v>280.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
@@ -12597,7 +12597,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" s="2">
-        <v>926.0</v>
+        <v>932.0</v>
       </c>
       <c r="K173" s="2">
         <v>1.0</v>
@@ -12609,19 +12609,19 @@
         <v>0.0</v>
       </c>
       <c r="N173" s="2">
-        <v>926.0</v>
+        <v>932.0</v>
       </c>
       <c r="O173" s="2">
-        <v>506.0</v>
+        <v>511.0</v>
       </c>
       <c r="P173" s="2">
-        <v>420.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q173" s="2">
         <v>0.0</v>
       </c>
       <c r="R173" s="2">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="S173" s="2">
         <v>8.0</v>
@@ -12636,7 +12636,7 @@
         <v>0.0</v>
       </c>
       <c r="W173" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -12739,7 +12739,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" s="2">
-        <v>1101.0</v>
+        <v>1144.0</v>
       </c>
       <c r="K175" s="2">
         <v>1.0</v>
@@ -12751,13 +12751,13 @@
         <v>0.0</v>
       </c>
       <c r="N175" s="2">
-        <v>1101.0</v>
+        <v>1144.0</v>
       </c>
       <c r="O175" s="2">
-        <v>507.0</v>
+        <v>521.0</v>
       </c>
       <c r="P175" s="2">
-        <v>594.0</v>
+        <v>623.0</v>
       </c>
       <c r="Q175" s="2">
         <v>0.0</v>
@@ -12766,7 +12766,7 @@
         <v>49.0</v>
       </c>
       <c r="S175" s="2">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="T175" s="2">
         <v>0.0</v>
@@ -12778,7 +12778,7 @@
         <v>0.0</v>
       </c>
       <c r="W175" s="2">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>621.0</v>
+        <v>626.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>621.0</v>
+        <v>626.0</v>
       </c>
       <c r="O176" s="2">
         <v>274.0</v>
       </c>
       <c r="P176" s="2">
-        <v>346.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q176" s="2">
         <v>1.0</v>
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>570.0</v>
+        <v>592.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>570.0</v>
+        <v>592.0</v>
       </c>
       <c r="O177" s="2">
-        <v>320.0</v>
+        <v>335.0</v>
       </c>
       <c r="P177" s="2">
-        <v>250.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -12952,7 +12952,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>526.0</v>
+        <v>556.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12964,13 +12964,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>526.0</v>
+        <v>556.0</v>
       </c>
       <c r="O178" s="2">
-        <v>238.0</v>
+        <v>256.0</v>
       </c>
       <c r="P178" s="2">
-        <v>287.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -12982,16 +12982,16 @@
         <v>7.0</v>
       </c>
       <c r="T178" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U178" s="2">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>725.0</v>
+        <v>732.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,10 +13035,10 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>725.0</v>
+        <v>732.0</v>
       </c>
       <c r="O179" s="2">
-        <v>447.0</v>
+        <v>454.0</v>
       </c>
       <c r="P179" s="2">
         <v>277.0</v>
@@ -13165,7 +13165,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>473.0</v>
+        <v>492.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13177,13 +13177,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>473.0</v>
+        <v>492.0</v>
       </c>
       <c r="O181" s="2">
-        <v>247.0</v>
+        <v>258.0</v>
       </c>
       <c r="P181" s="2">
-        <v>226.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
@@ -13378,7 +13378,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>541.0</v>
+        <v>576.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13390,22 +13390,22 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>540.0</v>
+        <v>575.0</v>
       </c>
       <c r="O184" s="2">
-        <v>257.0</v>
+        <v>276.0</v>
       </c>
       <c r="P184" s="2">
-        <v>283.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q184" s="2">
         <v>1.0</v>
       </c>
       <c r="R184" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="S184" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="T184" s="2">
         <v>4.0</v>
@@ -13417,7 +13417,7 @@
         <v>0.0</v>
       </c>
       <c r="W184" s="2">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -13449,7 +13449,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>762.0</v>
+        <v>798.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13461,22 +13461,22 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>762.0</v>
+        <v>798.0</v>
       </c>
       <c r="O185" s="2">
-        <v>401.0</v>
+        <v>427.0</v>
       </c>
       <c r="P185" s="2">
-        <v>361.0</v>
+        <v>371.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
       </c>
       <c r="R185" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="S185" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="T185" s="2">
         <v>1.0</v>
@@ -13488,7 +13488,7 @@
         <v>0.0</v>
       </c>
       <c r="W185" s="2">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>845.0</v>
+        <v>857.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,16 +13532,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>845.0</v>
+        <v>857.0</v>
       </c>
       <c r="O186" s="2">
-        <v>238.0</v>
+        <v>247.0</v>
       </c>
       <c r="P186" s="2">
-        <v>352.0</v>
+        <v>354.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="R186" s="2">
         <v>15.0</v>
@@ -13733,7 +13733,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>768.0</v>
+        <v>877.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13745,16 +13745,16 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>768.0</v>
+        <v>877.0</v>
       </c>
       <c r="O189" s="2">
-        <v>243.0</v>
+        <v>311.0</v>
       </c>
       <c r="P189" s="2">
-        <v>255.0</v>
+        <v>295.0</v>
       </c>
       <c r="Q189" s="2">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="R189" s="2">
         <v>1.0</v>
@@ -13804,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>1153.0</v>
+        <v>1168.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13816,22 +13816,22 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>1153.0</v>
+        <v>1168.0</v>
       </c>
       <c r="O190" s="2">
-        <v>675.0</v>
+        <v>683.0</v>
       </c>
       <c r="P190" s="2">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="Q190" s="2">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="R190" s="2">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="S190" s="2">
-        <v>55.0</v>
+        <v>65.0</v>
       </c>
       <c r="T190" s="2">
         <v>6.0</v>
@@ -13843,7 +13843,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" s="2">
-        <v>111.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -13875,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>918.0</v>
+        <v>1076.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13887,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>918.0</v>
+        <v>1076.0</v>
       </c>
       <c r="O191" s="2">
-        <v>504.0</v>
+        <v>612.0</v>
       </c>
       <c r="P191" s="2">
-        <v>381.0</v>
+        <v>431.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -14017,7 +14017,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1118.0</v>
+        <v>1124.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14029,13 +14029,13 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1118.0</v>
+        <v>1124.0</v>
       </c>
       <c r="O193" s="2">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
       <c r="P193" s="2">
-        <v>489.0</v>
+        <v>494.0</v>
       </c>
       <c r="Q193" s="2">
         <v>215.0</v>
@@ -14088,7 +14088,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" s="2">
-        <v>337.0</v>
+        <v>356.0</v>
       </c>
       <c r="K194" s="2">
         <v>1.0</v>
@@ -14100,13 +14100,13 @@
         <v>0.0</v>
       </c>
       <c r="N194" s="2">
-        <v>337.0</v>
+        <v>356.0</v>
       </c>
       <c r="O194" s="2">
-        <v>114.0</v>
+        <v>118.0</v>
       </c>
       <c r="P194" s="2">
-        <v>194.0</v>
+        <v>209.0</v>
       </c>
       <c r="Q194" s="2">
         <v>29.0</v>
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>440.0</v>
+        <v>455.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,13 +14171,13 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>440.0</v>
+        <v>455.0</v>
       </c>
       <c r="O195" s="2">
-        <v>147.0</v>
+        <v>152.0</v>
       </c>
       <c r="P195" s="2">
-        <v>167.0</v>
+        <v>177.0</v>
       </c>
       <c r="Q195" s="2">
         <v>126.0</v>
@@ -14186,7 +14186,7 @@
         <v>1.0</v>
       </c>
       <c r="S195" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T195" s="2">
         <v>0.0</v>
@@ -14198,7 +14198,7 @@
         <v>0.0</v>
       </c>
       <c r="W195" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
@@ -14372,7 +14372,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" s="2">
-        <v>1204.0</v>
+        <v>1252.0</v>
       </c>
       <c r="K198" s="2">
         <v>1.0</v>
@@ -14384,13 +14384,13 @@
         <v>0.0</v>
       </c>
       <c r="N198" s="2">
-        <v>1204.0</v>
+        <v>1252.0</v>
       </c>
       <c r="O198" s="2">
-        <v>337.0</v>
+        <v>360.0</v>
       </c>
       <c r="P198" s="2">
-        <v>592.0</v>
+        <v>617.0</v>
       </c>
       <c r="Q198" s="2">
         <v>275.0</v>
@@ -14399,7 +14399,7 @@
         <v>52.0</v>
       </c>
       <c r="S198" s="2">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="T198" s="2">
         <v>11.0</v>
@@ -14411,7 +14411,7 @@
         <v>0.0</v>
       </c>
       <c r="W198" s="2">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>564.0</v>
+        <v>567.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,13 +14526,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>564.0</v>
+        <v>567.0</v>
       </c>
       <c r="O200" s="2">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="P200" s="2">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14585,7 +14585,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>1028.0</v>
+        <v>1085.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14597,34 +14597,34 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>1028.0</v>
+        <v>1085.0</v>
       </c>
       <c r="O201" s="2">
-        <v>550.0</v>
+        <v>584.0</v>
       </c>
       <c r="P201" s="2">
-        <v>467.0</v>
+        <v>490.0</v>
       </c>
       <c r="Q201" s="2">
         <v>11.0</v>
       </c>
       <c r="R201" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="S201" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="T201" s="2">
         <v>4.0</v>
       </c>
       <c r="U201" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="V201" s="2">
         <v>1.0</v>
       </c>
       <c r="W201" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>770.0</v>
+        <v>784.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>770.0</v>
+        <v>784.0</v>
       </c>
       <c r="O202" s="2">
-        <v>455.0</v>
+        <v>463.0</v>
       </c>
       <c r="P202" s="2">
-        <v>315.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14751,10 +14751,10 @@
         <v>1.0</v>
       </c>
       <c r="R203" s="2">
-        <v>54.0</v>
+        <v>68.0</v>
       </c>
       <c r="S203" s="2">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
       <c r="T203" s="2">
         <v>5.0</v>
@@ -14766,7 +14766,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>82.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14798,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>790.0</v>
+        <v>857.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14810,13 +14810,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>790.0</v>
+        <v>857.0</v>
       </c>
       <c r="O204" s="2">
-        <v>430.0</v>
+        <v>461.0</v>
       </c>
       <c r="P204" s="2">
-        <v>351.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q204" s="2">
         <v>9.0</v>
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>641.0</v>
+        <v>655.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,13 +14881,13 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>641.0</v>
+        <v>655.0</v>
       </c>
       <c r="O205" s="2">
-        <v>332.0</v>
+        <v>339.0</v>
       </c>
       <c r="P205" s="2">
-        <v>268.0</v>
+        <v>275.0</v>
       </c>
       <c r="Q205" s="2">
         <v>41.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>743.0</v>
+        <v>754.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,10 +14952,10 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>743.0</v>
+        <v>754.0</v>
       </c>
       <c r="O206" s="2">
-        <v>467.0</v>
+        <v>478.0</v>
       </c>
       <c r="P206" s="2">
         <v>276.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>593.0</v>
+        <v>608.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>593.0</v>
+        <v>608.0</v>
       </c>
       <c r="O207" s="2">
-        <v>332.0</v>
+        <v>342.0</v>
       </c>
       <c r="P207" s="2">
-        <v>251.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q207" s="2">
         <v>10.0</v>
@@ -15180,7 +15180,7 @@
         <v>47.0</v>
       </c>
       <c r="S209" s="2">
-        <v>27.0</v>
+        <v>55.0</v>
       </c>
       <c r="T209" s="2">
         <v>6.0</v>
@@ -15192,7 +15192,7 @@
         <v>1.0</v>
       </c>
       <c r="W209" s="2">
-        <v>81.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15295,7 +15295,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>863.0</v>
+        <v>873.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15307,22 +15307,22 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>863.0</v>
+        <v>873.0</v>
       </c>
       <c r="O211" s="2">
-        <v>446.0</v>
+        <v>450.0</v>
       </c>
       <c r="P211" s="2">
         <v>417.0</v>
       </c>
       <c r="Q211" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="R211" s="2">
         <v>66.0</v>
       </c>
       <c r="S211" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="T211" s="2">
         <v>5.0</v>
@@ -15334,7 +15334,7 @@
         <v>0.0</v>
       </c>
       <c r="W211" s="2">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
@@ -15366,7 +15366,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" s="2">
-        <v>802.0</v>
+        <v>816.0</v>
       </c>
       <c r="K212" s="2">
         <v>1.0</v>
@@ -15378,10 +15378,10 @@
         <v>1.0</v>
       </c>
       <c r="N212" s="2">
-        <v>801.0</v>
+        <v>815.0</v>
       </c>
       <c r="O212" s="2">
-        <v>210.0</v>
+        <v>224.0</v>
       </c>
       <c r="P212" s="2">
         <v>372.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>776.0</v>
+        <v>803.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>776.0</v>
+        <v>803.0</v>
       </c>
       <c r="O213" s="2">
-        <v>443.0</v>
+        <v>455.0</v>
       </c>
       <c r="P213" s="2">
-        <v>333.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>953.0</v>
+        <v>954.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,10 +15591,10 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>953.0</v>
+        <v>954.0</v>
       </c>
       <c r="O215" s="2">
-        <v>483.0</v>
+        <v>484.0</v>
       </c>
       <c r="P215" s="2">
         <v>461.0</v>
@@ -15792,7 +15792,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>699.0</v>
+        <v>704.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15804,19 +15804,19 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>698.0</v>
+        <v>703.0</v>
       </c>
       <c r="O218" s="2">
-        <v>356.0</v>
+        <v>359.0</v>
       </c>
       <c r="P218" s="2">
-        <v>343.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="S218" s="2">
         <v>12.0</v>
@@ -15831,7 +15831,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>957.0</v>
+        <v>970.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,22 +15875,22 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>957.0</v>
+        <v>970.0</v>
       </c>
       <c r="O219" s="2">
-        <v>169.0</v>
+        <v>174.0</v>
       </c>
       <c r="P219" s="2">
-        <v>410.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="R219" s="2">
         <v>24.0</v>
       </c>
       <c r="S219" s="2">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="T219" s="2">
         <v>3.0</v>
@@ -15902,7 +15902,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -16005,7 +16005,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>728.0</v>
+        <v>747.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16017,13 +16017,13 @@
         <v>1.0</v>
       </c>
       <c r="N221" s="2">
-        <v>727.0</v>
+        <v>746.0</v>
       </c>
       <c r="O221" s="2">
-        <v>204.0</v>
+        <v>219.0</v>
       </c>
       <c r="P221" s="2">
-        <v>277.0</v>
+        <v>281.0</v>
       </c>
       <c r="Q221" s="2">
         <v>247.0</v>
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>724.0</v>
+        <v>760.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,13 +16088,13 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>724.0</v>
+        <v>760.0</v>
       </c>
       <c r="O222" s="2">
-        <v>179.0</v>
+        <v>198.0</v>
       </c>
       <c r="P222" s="2">
-        <v>309.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q222" s="2">
         <v>236.0</v>
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>852.0</v>
+        <v>868.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,7 +16159,7 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>852.0</v>
+        <v>868.0</v>
       </c>
       <c r="O223" s="2">
         <v>101.0</v>
@@ -16168,7 +16168,7 @@
         <v>277.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>474.0</v>
+        <v>490.0</v>
       </c>
       <c r="R223" s="2">
         <v>71.0</v>
@@ -16218,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>581.0</v>
+        <v>593.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16230,7 +16230,7 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>581.0</v>
+        <v>593.0</v>
       </c>
       <c r="O224" s="2">
         <v>22.0</v>
@@ -16239,7 +16239,7 @@
         <v>38.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>521.0</v>
+        <v>533.0</v>
       </c>
       <c r="R224" s="2">
         <v>2.0</v>
@@ -16360,7 +16360,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>835.0</v>
+        <v>840.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16372,13 +16372,13 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>835.0</v>
+        <v>840.0</v>
       </c>
       <c r="O226" s="2">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="P226" s="2">
-        <v>373.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q226" s="2">
         <v>327.0</v>
@@ -16502,7 +16502,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>907.0</v>
+        <v>928.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16514,19 +16514,19 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>907.0</v>
+        <v>928.0</v>
       </c>
       <c r="O228" s="2">
-        <v>223.0</v>
+        <v>230.0</v>
       </c>
       <c r="P228" s="2">
-        <v>355.0</v>
+        <v>368.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="R228" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="S228" s="2">
         <v>5.0</v>
@@ -16541,7 +16541,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>821.0</v>
+        <v>832.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,13 +16798,13 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>821.0</v>
+        <v>832.0</v>
       </c>
       <c r="O232" s="2">
-        <v>53.0</v>
+        <v>61.0</v>
       </c>
       <c r="P232" s="2">
-        <v>151.0</v>
+        <v>154.0</v>
       </c>
       <c r="Q232" s="2">
         <v>617.0</v>
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>536.0</v>
+        <v>549.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,16 +16869,16 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>536.0</v>
+        <v>549.0</v>
       </c>
       <c r="O233" s="2">
-        <v>137.0</v>
+        <v>149.0</v>
       </c>
       <c r="P233" s="2">
         <v>254.0</v>
       </c>
       <c r="Q233" s="2">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="R233" s="2">
         <v>7.0</v>
